--- a/robokidy_billing_data.xlsx
+++ b/robokidy_billing_data.xlsx
@@ -11,7 +11,9 @@
     <sheet name="Students" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Invoices" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Payments" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Settings" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="CoursePlans" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Finance" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Settings" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -449,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -471,7 +473,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>03-06-2026 10:36 AM</t>
+          <t>04-06-2026 09:56 AM</t>
         </is>
       </c>
     </row>
@@ -482,7 +484,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -492,7 +494,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +504,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -512,7 +514,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-63000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -522,7 +524,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -532,7 +534,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-70000</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Total Income</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Total Expenses</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net Profit</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -546,7 +578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -637,73 +669,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>RK-SC-L2-2026-001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>NIVIIN</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>BALA</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>12433</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>BALA</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Scratch</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Level 2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Afternoon</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>03-06-2026</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>22222</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -715,7 +680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -848,87 +813,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>RKI-INV-2026-0001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>03-06-2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>RK-SC-L2-2026-001</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>NIVIIN</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Scratch</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Level 2</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Afternoon</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>7000</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>70000</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-63000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>7000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-70000</v>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>Cash</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -940,7 +824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1001,57 +885,494 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>RKI-RCP-2026-0001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>03-06-2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>RKI-INV-2026-0001</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>RK-SC-L2-2026-001</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>NIVIIN</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Cash</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>7000</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Initial payment</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Plan ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Course</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Fee</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PLN-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Level 1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Python basics</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PLN-002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Level 2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Python advanced</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PLN-003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Robotics</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Level 1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3500</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Robotics basics</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PLN-004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Arduino</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Level 1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Arduino basics</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PLN-005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Scratch</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Level 1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Scratch basics</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PLN-006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Level 1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>AI/ML monthly</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PLN-007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Level 1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>3500</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>IoT monthly</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PLN-008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Web Dev</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Level 1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Web Dev monthly</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PLN-009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Yearly All-Courses</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Yearly</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>All courses yearly plan</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PLN-010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Yearly All-Courses</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Half-Yearly</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>14000</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>All courses half-yearly</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Entry ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Payment Mode</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/robokidy_billing_data.xlsx
+++ b/robokidy_billing_data.xlsx
@@ -14,6 +14,7 @@
     <sheet name="CoursePlans" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Finance" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Settings" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Courses" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -80,12 +81,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -473,7 +477,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>04-06-2026 09:56 AM</t>
+          <t>05-06-2026 04:25 PM</t>
         </is>
       </c>
     </row>
@@ -484,7 +488,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -494,7 +498,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -504,7 +508,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -514,7 +518,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="8">
@@ -524,7 +528,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="9">
@@ -534,7 +538,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="11">
@@ -544,7 +548,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="12">
@@ -564,7 +568,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
     </row>
   </sheetData>
@@ -578,23 +582,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -668,6 +672,110 @@
           <t>Notes</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>RK-LG-L1-2026-001</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>bala</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr"/>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Lego</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Level 1</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Morning</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>05-06-2026</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr"/>
+      <c r="N2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>RK-OT-L1-2026-001</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>ASRITTH</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>OT</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Level 1</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Morning</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>05-06-2026</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -680,30 +788,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U1"/>
+  <dimension ref="A1:U3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -812,6 +920,172 @@
           <t>Notes</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>RKI-INV-2026-0001</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>05-06-2026</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>RK-LG-L1-2026-001</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>bala</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Lego</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Level 1</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Morning</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>2500</v>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="R2" s="3" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr"/>
+      <c r="U2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>RKI-INV-2026-0002</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>05-06-2026</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>RK-OT-L1-2026-001</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>ASRITTH</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Level 1</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Morning</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>3500</v>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>3500</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -824,18 +1098,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -882,6 +1161,205 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Total Fees</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Fees Paid</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Balance Fees</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Receipt Paid</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Payment Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>RKI-RCP-2026-0001</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>05-06-2026</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>RKI-INV-2026-0001</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>RK-LG-L1-2026-001</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>bala</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr"/>
+      <c r="J2" s="3" t="n">
+        <v>2500</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>RKI-RCP-2026-0002</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>05-06-2026</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>RKI-INV-2026-0002</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>RK-OT-L1-2026-001</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>ASRITTH</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="n">
+        <v>3500</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>RKI-RCP-2026-0003</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>05-06-2026</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>RKI-INV-2026-0001</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>RK-LG-L1-2026-001</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>bala</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="n">
+        <v>2500</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
     </row>
@@ -896,16 +1374,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -946,350 +1424,381 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>PLN-001</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Level 1</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="3" t="n">
         <v>2500</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Python basics</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>PLN-002</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Level 2</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Python advanced</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>PLN-003</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Robotics</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Level 1</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="3" t="n">
         <v>3500</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Robotics basics</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>PLN-004</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Arduino</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Level 1</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Arduino basics</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>PLN-005</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Scratch</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Level 1</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>Scratch basics</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>PLN-006</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>AI/ML</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Level 1</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="3" t="n">
         <v>4000</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>AI/ML monthly</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>PLN-007</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>IoT</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Level 1</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="3" t="n">
         <v>3500</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>IoT monthly</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>PLN-008</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Web Dev</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Level 1</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Web Dev monthly</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>PLN-009</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Yearly All-Courses</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>All Levels</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Yearly</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="3" t="n">
         <v>25000</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>All courses yearly plan</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>PLN-010</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Yearly All-Courses</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>All Levels</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Half-Yearly</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="3" t="n">
         <v>14000</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>All courses half-yearly</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>PLN-0011</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>CYBERPI</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Level 1</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>2 Month</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>3500</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr"/>
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1306,18 +1815,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1366,6 +1875,129 @@
           <t>Notes</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>FIN-2026-0001</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>05-06-2026</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Course Fee</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Fee payment from bala</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>RKI-RCP-2026-0001</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>FIN-2026-0002</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>05-06-2026</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Course Fee</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Fee payment from ASRITTH</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>RKI-RCP-2026-0002</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>FIN-2026-0003</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>05-06-2026</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Course Fee</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Fee payment from bala</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>RKI-RCP-2026-0003</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1381,8 +2013,8 @@
   <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1398,98 +2030,151 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Company Name</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Robokidy Innovative Centre</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Address</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>91/3 Ramachandra Nagar, Kallakurichi</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>+91 8300967241</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>info@robokidy.com</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>www.robokidy.com</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>GSTIN</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>33AAOCR3798M1Z1</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Invoice Prefix</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>RKI-INV</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Receipt Prefix</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>RKI-RCP</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Course</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Course Code</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Deep learning</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
